--- a/weight-heatmap-mock.xlsx
+++ b/weight-heatmap-mock.xlsx
@@ -343,7 +343,7 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Heat scale: 0% grey · 5% green · ~50% yellow · 100% red (Conditional Formatting applied to column G).</t>
+          <t xml:space="preserve">Heat scale (Conditional Formatting on col G): grey=empty · green=filling · yellow=28,000 lb dispatch floor (70%) · red=40,000 lb cube-out.</t>
         </is>
       </c>
     </row>
@@ -355,7 +355,7 @@
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.05"/>
-        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.70"/>
         <cfvo type="num" val="1"/>
         <color rgb="FF38A169"/>
         <color rgb="FFF6E05E"/>
